--- a/backend/data/financials_by_company/0197.HK.xlsx
+++ b/backend/data/financials_by_company/0197.HK.xlsx
@@ -3758,182 +3758,182 @@
       </c>
       <c r="DB1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -4036,28 +4036,28 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3</v>
+        <v>0.295</v>
       </c>
       <c r="V2" t="n">
-        <v>0.285</v>
+        <v>0.295</v>
       </c>
       <c r="W2" t="n">
-        <v>0.28</v>
+        <v>0.295</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3</v>
+        <v>0.295</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.285</v>
+        <v>0.295</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.28</v>
+        <v>0.295</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="AC2" t="n">
         <v>1292889600</v>
@@ -4066,28 +4066,28 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.004</v>
+        <v>-0.019</v>
       </c>
       <c r="AF2" t="n">
-        <v>331805</v>
+        <v>90000</v>
       </c>
       <c r="AG2" t="n">
-        <v>331805</v>
+        <v>90000</v>
       </c>
       <c r="AH2" t="n">
-        <v>136897</v>
+        <v>299634</v>
       </c>
       <c r="AI2" t="n">
-        <v>40350</v>
+        <v>1106156</v>
       </c>
       <c r="AJ2" t="n">
-        <v>40350</v>
+        <v>1106156</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.315</v>
+        <v>0.325</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -4096,13 +4096,13 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>60671028</v>
+        <v>64855240</v>
       </c>
       <c r="AP2" t="n">
-        <v>62763135</v>
+        <v>57532874</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.166</v>
+        <v>0.172</v>
       </c>
       <c r="AR2" t="n">
         <v>0.7</v>
@@ -4114,13 +4114,13 @@
         <v>0.12</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.17434905</v>
+        <v>0.18637314</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.2901</v>
+        <v>0.2927</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.33099</v>
+        <v>0.32489</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -4137,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-74806968</v>
+        <v>-70622760</v>
       </c>
       <c r="BC2" t="n">
         <v>-0.57556</v>
@@ -4149,7 +4149,7 @@
         <v>209210453</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.44961</v>
+        <v>0.43493</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -4161,7 +4161,7 @@
         <v>2.676</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.10837069</v>
+        <v>0.11584454</v>
       </c>
       <c r="BK2" t="n">
         <v>1751241600</v>
@@ -4176,7 +4176,7 @@
         <v>-200288000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-1.11</v>
+        <v>-1.12</v>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
@@ -4187,16 +4187,16 @@
         <v>1703721600</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0.215</v>
+        <v>-0.203</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.009</v>
+        <v>0.953</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.52284265</v>
+        <v>0.63888884</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="BV2" t="n">
         <v>1.43332</v>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="BY2" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
@@ -4314,135 +4314,135 @@
           <t>HENG TAI</t>
         </is>
       </c>
-      <c r="DB2" t="n">
-        <v>-3.33334</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>Heng Tai Consumables Group Limited</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>1007343000000</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>0.0150000155</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>0.295 - 0.31</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>299634</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>0.8023255500000001</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>0.172 - 0.7</t>
+        </is>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>-0.55714285</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>63.888885</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>1740737475</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1740737475</v>
+      </c>
+      <c r="DR2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.01730001</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.05910492</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.014889985</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-0.045830853</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EB2" t="n">
+        <v>1783066093</v>
+      </c>
+      <c r="EC2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
         <is>
           <t>finmb_5397526</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="EE2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="EF2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DI2" t="n">
+      <c r="EG2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="EH2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>136897</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>0.74698794</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>0.166 - 0.7</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.5857143</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>52.284264</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>1740737475</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>1740737475</v>
-      </c>
-      <c r="DV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-1.11</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.000100016594</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.00034476593</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.040989995</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.12384059</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EE2" t="n">
-        <v>1782097882</v>
-      </c>
-      <c r="EF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>1007343000000</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-0.01000002</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>0.28 - 0.3</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>Heng Tai Consumables Group Limited</t>
-        </is>
+      <c r="EI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>5.084751</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>0.31</v>
       </c>
       <c r="EL2" t="inlineStr"/>
     </row>
